--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WT.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_WT.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R72babce86c6f4a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Re7bc514761504896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R309c3c7d48454959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R4817fe868a4e4072"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rebc5ef1c337c4707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R5c1c76edfa114ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R986f745569d94347"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rf6c8aacfc8cd4d7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R899eb3baa62743b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R61c6c2167a524896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Ra6035285dd5a4c81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rf425bf5871a24dc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rfd70c861ce064bdd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R25b9d409b4604720"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R5901f264f56f4edc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R0a601beae03a43f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R728e0c56a02f4e73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rb2874de807f54081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rafce61da0a1842c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Ra3561e84d12140a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Ra82d83fd3f1346fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R50b34ceed4a24e9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R2bc9107b95de4389"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Ra3c0ddf44f9247ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Re9b5906f70de47af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Ra932dd4d276c4b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R3cd28f2f028d4056"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R8a398d2e244b4afe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Re5fcea8ac2fa458b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R6a18547513814fcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R314d912fdff84a98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rd33db5c5459d4102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R0735ed8aac414331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="Rd2279da2c08a4914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Ra1ef71d542d14066"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R33c055f3aca04ef4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R6f7dddf1762f4500"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Re99b8084c04f4b96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R8d836ce7e7a34aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rccbfae3fbd8043b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rea2aaf3cc37d460a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rcc235b67e3944d22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R79e4c5da0cea4a5d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4234,6 +4235,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>ローズ・ジン・グランフォード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>ラブリフ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
